--- a/src/assets/samples/Import Update Device.xlsx
+++ b/src/assets/samples/Import Update Device.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Afaqy\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Afaqy\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B2CB5F-D8D9-4D0F-AEFE-F89AD12F410A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F9B37C-D5A8-46C7-B0CF-FD66BE1C54A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3072" yWindow="3072" windowWidth="17280" windowHeight="9960" xr2:uid="{D50E93A1-DE92-4778-8A30-60E51C386C67}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D50E93A1-DE92-4778-8A30-60E51C386C67}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Old Serial</t>
   </si>
@@ -47,9 +47,6 @@
     <t>Device Condition</t>
   </si>
   <si>
-    <t>ErrandChannel</t>
-  </si>
-  <si>
     <t>ShipmentId</t>
   </si>
   <si>
@@ -66,13 +63,25 @@
   </si>
   <si>
     <t>Warehouse ID</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Bank</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Notes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,39 +100,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF414141"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Public Sans"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF414141"/>
-      <name val="Public Sans"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF414141"/>
-      <name val="Public-sans"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -139,24 +122,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -492,22 +462,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EECAAD5-535E-4163-A8F9-1F4819760B1E}">
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -518,38 +491,35 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="17.399999999999999">
-      <c r="A2" s="2"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="1"/>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
